--- a/plot/storage/output/ongoing/ongoing_tech_filter_by_iso2_q.xlsx
+++ b/plot/storage/output/ongoing/ongoing_tech_filter_by_iso2_q.xlsx
@@ -571,7 +571,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>121616428.5714286</v>
+        <v>86616428.57142857</v>
       </c>
       <c r="H2" t="n">
         <v>9166666.666666666</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>133074761.9047619</v>
+        <v>94185873.01587301</v>
       </c>
       <c r="H3" t="n">
         <v>9166666.666666666</v>
@@ -713,7 +713,7 @@
         <v>18333333.33333333</v>
       </c>
       <c r="G4" t="n">
-        <v>155991428.5714286</v>
+        <v>109324761.9047619</v>
       </c>
       <c r="H4" t="n">
         <v>9166666.666666666</v>
@@ -784,7 +784,7 @@
         <v>55000000</v>
       </c>
       <c r="G5" t="n">
-        <v>155991428.5714286</v>
+        <v>109324761.9047619</v>
       </c>
       <c r="H5" t="n">
         <v>21388888.88888889</v>
@@ -793,7 +793,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>12422222.22222222</v>
+        <v>5755555.555555555</v>
       </c>
       <c r="K5" t="n">
         <v>27500000</v>
@@ -855,7 +855,7 @@
         <v>55000000</v>
       </c>
       <c r="G6" t="n">
-        <v>100991428.5714286</v>
+        <v>89324761.90476191</v>
       </c>
       <c r="H6" t="n">
         <v>82500000</v>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>36866666.66666666</v>
+        <v>23533333.33333333</v>
       </c>
       <c r="K6" t="n">
         <v>18333333.33333333</v>
@@ -926,7 +926,7 @@
         <v>55000000</v>
       </c>
       <c r="G7" t="n">
-        <v>99991428.57142857</v>
+        <v>88324761.90476191</v>
       </c>
       <c r="H7" t="n">
         <v>82500000</v>
@@ -935,7 +935,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>36866666.66666666</v>
+        <v>23533333.33333333</v>
       </c>
       <c r="K7" t="n">
         <v>18333333.33333333</v>
@@ -997,7 +997,7 @@
         <v>57224255.83333333</v>
       </c>
       <c r="G8" t="n">
-        <v>119201984.1269841</v>
+        <v>107535317.4603175</v>
       </c>
       <c r="H8" t="n">
         <v>82500000</v>
@@ -1006,7 +1006,7 @@
         <v>3333333.333333333</v>
       </c>
       <c r="J8" t="n">
-        <v>36866666.66666666</v>
+        <v>23533333.33333333</v>
       </c>
       <c r="K8" t="n">
         <v>18333333.33333333</v>
@@ -1068,7 +1068,7 @@
         <v>61672767.49999999</v>
       </c>
       <c r="G9" t="n">
-        <v>269928884.7117795</v>
+        <v>258262218.0451128</v>
       </c>
       <c r="H9" t="n">
         <v>82500000</v>
@@ -1077,7 +1077,7 @@
         <v>10000000</v>
       </c>
       <c r="J9" t="n">
-        <v>59783333.33333333</v>
+        <v>27700000</v>
       </c>
       <c r="K9" t="n">
         <v>18333333.33333333</v>
@@ -1139,7 +1139,7 @@
         <v>61672767.49999999</v>
       </c>
       <c r="G10" t="n">
-        <v>298205827.0676692</v>
+        <v>286539160.4010025</v>
       </c>
       <c r="H10" t="n">
         <v>119166666.6666667</v>
@@ -1148,7 +1148,7 @@
         <v>10000000</v>
       </c>
       <c r="J10" t="n">
-        <v>105616666.6666667</v>
+        <v>36033333.33333333</v>
       </c>
       <c r="K10" t="n">
         <v>18333333.33333333</v>
@@ -1210,7 +1210,7 @@
         <v>68894989.72222221</v>
       </c>
       <c r="G11" t="n">
-        <v>291480628.6549708</v>
+        <v>279813961.9883041</v>
       </c>
       <c r="H11" t="n">
         <v>116111111.1111111</v>
@@ -1219,7 +1219,7 @@
         <v>10000000</v>
       </c>
       <c r="J11" t="n">
-        <v>105616666.6666667</v>
+        <v>36033333.33333333</v>
       </c>
       <c r="K11" t="n">
         <v>18333333.33333333</v>
@@ -1281,7 +1281,7 @@
         <v>102573916.9583333</v>
       </c>
       <c r="G12" t="n">
-        <v>313744517.5438597</v>
+        <v>302077850.877193</v>
       </c>
       <c r="H12" t="n">
         <v>110000000</v>
@@ -1290,7 +1290,7 @@
         <v>10000000</v>
       </c>
       <c r="J12" t="n">
-        <v>105616666.6666667</v>
+        <v>36033333.33333333</v>
       </c>
       <c r="K12" t="n">
         <v>18333333.33333333</v>
@@ -1352,7 +1352,7 @@
         <v>102573916.9583333</v>
       </c>
       <c r="G13" t="n">
-        <v>618054508.2067914</v>
+        <v>606387841.5401248</v>
       </c>
       <c r="H13" t="n">
         <v>110000000</v>
@@ -1361,7 +1361,7 @@
         <v>10000000</v>
       </c>
       <c r="J13" t="n">
-        <v>105616666.6666667</v>
+        <v>39366666.66666666</v>
       </c>
       <c r="K13" t="n">
         <v>12222222.22222222</v>
@@ -1423,7 +1423,7 @@
         <v>92551311.58333333</v>
       </c>
       <c r="G14" t="n">
-        <v>1388047415.626169</v>
+        <v>1376380748.959503</v>
       </c>
       <c r="H14" t="n">
         <v>110000000</v>
@@ -1432,7 +1432,7 @@
         <v>21111111.11111111</v>
       </c>
       <c r="J14" t="n">
-        <v>106727777.7777778</v>
+        <v>47144444.44444444</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>72506100.83333333</v>
       </c>
       <c r="G15" t="n">
-        <v>1379888997.000438</v>
+        <v>1372111219.222661</v>
       </c>
       <c r="H15" t="n">
         <v>110000000</v>
@@ -1503,7 +1503,7 @@
         <v>43333333.33333334</v>
       </c>
       <c r="J15" t="n">
-        <v>108816666.6666667</v>
+        <v>49233333.33333333</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>43333333.33333334</v>
       </c>
       <c r="J16" t="n">
-        <v>108750000</v>
+        <v>49166666.66666666</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>43333333.33333334</v>
       </c>
       <c r="J17" t="n">
-        <v>108750000</v>
+        <v>46666666.66666666</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>43333333.33333334</v>
       </c>
       <c r="J18" t="n">
-        <v>108750000</v>
+        <v>41666666.66666666</v>
       </c>
       <c r="K18" t="n">
         <v>147392290</v>
@@ -1787,7 +1787,7 @@
         <v>43333333.33333334</v>
       </c>
       <c r="J19" t="n">
-        <v>108750000</v>
+        <v>41666666.66666666</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1858,7 +1858,7 @@
         <v>40000000</v>
       </c>
       <c r="J20" t="n">
-        <v>157638888.8888889</v>
+        <v>78333333.33333333</v>
       </c>
       <c r="K20" t="n">
         <v>32468305.63636363</v>
@@ -1929,7 +1929,7 @@
         <v>33333333.33333334</v>
       </c>
       <c r="J21" t="n">
-        <v>214166666.6666667</v>
+        <v>147500000</v>
       </c>
       <c r="K21" t="n">
         <v>91612761.38636363</v>
@@ -2000,7 +2000,7 @@
         <v>33333333.33333334</v>
       </c>
       <c r="J22" t="n">
-        <v>168333333.3333333</v>
+        <v>139166666.6666667</v>
       </c>
       <c r="K22" t="n">
         <v>91612761.38636363</v>
@@ -2071,7 +2071,7 @@
         <v>33333333.33333334</v>
       </c>
       <c r="J23" t="n">
-        <v>364487179.4871795</v>
+        <v>335320512.8205128</v>
       </c>
       <c r="K23" t="n">
         <v>81019159.50757575</v>
@@ -2142,7 +2142,7 @@
         <v>33333333.33333334</v>
       </c>
       <c r="J24" t="n">
-        <v>364487179.4871795</v>
+        <v>335320512.8205128</v>
       </c>
       <c r="K24" t="n">
         <v>99722848.30555555</v>
@@ -2213,7 +2213,7 @@
         <v>33333333.33333334</v>
       </c>
       <c r="J25" t="n">
-        <v>336153846.1538461</v>
+        <v>303653846.1538461</v>
       </c>
       <c r="K25" t="n">
         <v>125421300.0833333</v>
@@ -2284,7 +2284,7 @@
         <v>22222222.22222222</v>
       </c>
       <c r="J26" t="n">
-        <v>265876068.3760684</v>
+        <v>226709401.7094017</v>
       </c>
       <c r="K26" t="n">
         <v>127620574.4722222</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>172884615.3846154</v>
+        <v>133717948.7179487</v>
       </c>
       <c r="K27" t="n">
         <v>128720211.6666667</v>
@@ -2423,10 +2423,10 @@
         <v>681111111.111111</v>
       </c>
       <c r="I28" t="n">
-        <v>44444444.44444445</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>188340277.7777778</v>
+        <v>148638888.8888889</v>
       </c>
       <c r="K28" t="n">
         <v>128720211.6666667</v>
@@ -2494,10 +2494,10 @@
         <v>681111111.111111</v>
       </c>
       <c r="I29" t="n">
-        <v>66666666.66666667</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>342140716.374269</v>
+        <v>283036549.7076024</v>
       </c>
       <c r="K29" t="n">
         <v>128720211.6666667</v>
@@ -2565,10 +2565,10 @@
         <v>681111111.111111</v>
       </c>
       <c r="I30" t="n">
-        <v>66666666.66666667</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>449450657.8947369</v>
+        <v>347013157.8947368</v>
       </c>
       <c r="K30" t="n">
         <v>387479203.5555556</v>
@@ -2636,10 +2636,10 @@
         <v>837602339.1812865</v>
       </c>
       <c r="I31" t="n">
-        <v>66666666.66666667</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>466117324.5614035</v>
+        <v>363679824.5614035</v>
       </c>
       <c r="K31" t="n">
         <v>516858699.5000001</v>
@@ -2707,10 +2707,10 @@
         <v>922913336.5146199</v>
       </c>
       <c r="I32" t="n">
-        <v>66666666.66666667</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>398895102.3391813</v>
+        <v>363679824.5614035</v>
       </c>
       <c r="K32" t="n">
         <v>536170007.0833334</v>
@@ -2778,10 +2778,10 @@
         <v>922913336.5146199</v>
       </c>
       <c r="I33" t="n">
-        <v>66666666.66666667</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>365283991.2280702</v>
+        <v>363679824.5614035</v>
       </c>
       <c r="K33" t="n">
         <v>477025551.3333333</v>
@@ -2849,10 +2849,10 @@
         <v>907913336.5146199</v>
       </c>
       <c r="I34" t="n">
-        <v>66666666.66666667</v>
+        <v>22222222.22222222</v>
       </c>
       <c r="J34" t="n">
-        <v>365283991.2280702</v>
+        <v>363679824.5614035</v>
       </c>
       <c r="K34" t="n">
         <v>477025551.3333333</v>
@@ -2879,7 +2879,7 @@
         <v>39433383.76515152</v>
       </c>
       <c r="S34" t="n">
-        <v>19833333.33333333</v>
+        <v>130944444.4444444</v>
       </c>
       <c r="T34" t="n">
         <v>52500000</v>
@@ -2923,7 +2923,7 @@
         <v>66666666.66666667</v>
       </c>
       <c r="J35" t="n">
-        <v>301529605.2631579</v>
+        <v>299925438.5964912</v>
       </c>
       <c r="K35" t="n">
         <v>476796384.6666666</v>
@@ -2932,7 +2932,7 @@
         <v>8333333.333333334</v>
       </c>
       <c r="M35" t="n">
-        <v>1059502650.307315</v>
+        <v>1098391539.196204</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>32766717.09848485</v>
       </c>
       <c r="S35" t="n">
-        <v>65666666.66666666</v>
+        <v>232333333.3333333</v>
       </c>
       <c r="T35" t="n">
         <v>39722222.22222222</v>
@@ -2994,7 +2994,7 @@
         <v>66666666.66666667</v>
       </c>
       <c r="J36" t="n">
-        <v>44687500</v>
+        <v>43083333.33333333</v>
       </c>
       <c r="K36" t="n">
         <v>436447158.7777778</v>
@@ -3003,7 +3003,7 @@
         <v>2777777.777777778</v>
       </c>
       <c r="M36" t="n">
-        <v>1205462303.399321</v>
+        <v>1263795636.732655</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
         <v>7312171.643939395</v>
       </c>
       <c r="S36" t="n">
-        <v>65666666.66666666</v>
+        <v>232333333.3333333</v>
       </c>
       <c r="T36" t="n">
         <v>33333333.33333334</v>

--- a/plot/storage/output/ongoing/ongoing_tech_filter_by_iso2_q.xlsx
+++ b/plot/storage/output/ongoing/ongoing_tech_filter_by_iso2_q.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,110 +442,105 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>GR</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
@@ -568,28 +563,28 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>86616428.57142857</v>
       </c>
       <c r="G2" t="n">
-        <v>86616428.57142857</v>
+        <v>9166666.666666666</v>
       </c>
       <c r="H2" t="n">
-        <v>9166666.666666666</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>77808392.97222221</v>
       </c>
       <c r="K2" t="n">
-        <v>77808392.97222221</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>133612643.6666667</v>
       </c>
       <c r="M2" t="n">
-        <v>133612643.6666667</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -598,10 +593,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -616,9 +611,6 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
         <v>45833333.33333334</v>
       </c>
     </row>
@@ -639,28 +631,28 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>94185873.01587301</v>
       </c>
       <c r="G3" t="n">
-        <v>94185873.01587301</v>
+        <v>9166666.666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>9166666.666666666</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>133333.3333333333</v>
       </c>
       <c r="J3" t="n">
-        <v>133333.3333333333</v>
+        <v>58326608.41666666</v>
       </c>
       <c r="K3" t="n">
-        <v>58326608.41666666</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>35630399.33333334</v>
       </c>
       <c r="M3" t="n">
-        <v>35630399.33333334</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -669,10 +661,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -687,9 +679,6 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
         <v>45833333.33333334</v>
       </c>
     </row>
@@ -707,25 +696,25 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>18333333.33333333</v>
       </c>
       <c r="F4" t="n">
-        <v>18333333.33333333</v>
+        <v>109324761.9047619</v>
       </c>
       <c r="G4" t="n">
-        <v>109324761.9047619</v>
+        <v>9166666.666666666</v>
       </c>
       <c r="H4" t="n">
-        <v>9166666.666666666</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="J4" t="n">
-        <v>200000</v>
+        <v>27500000</v>
       </c>
       <c r="K4" t="n">
-        <v>27500000</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -740,10 +729,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -758,9 +747,6 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
         <v>45833333.33333334</v>
       </c>
     </row>
@@ -778,25 +764,25 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>55000000</v>
       </c>
       <c r="F5" t="n">
-        <v>55000000</v>
+        <v>109324761.9047619</v>
       </c>
       <c r="G5" t="n">
-        <v>109324761.9047619</v>
+        <v>21388888.88888889</v>
       </c>
       <c r="H5" t="n">
-        <v>21388888.88888889</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5755555.555555555</v>
       </c>
       <c r="J5" t="n">
-        <v>5755555.555555555</v>
+        <v>27500000</v>
       </c>
       <c r="K5" t="n">
-        <v>27500000</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -811,13 +797,13 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1000000</v>
+        <v>107255082.75</v>
       </c>
       <c r="R5" t="n">
-        <v>107255082.75</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -826,12 +812,9 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>6111111.111111111</v>
       </c>
       <c r="V5" t="n">
-        <v>6111111.111111111</v>
-      </c>
-      <c r="W5" t="n">
         <v>55000000</v>
       </c>
     </row>
@@ -849,60 +832,57 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>55000000</v>
       </c>
       <c r="F6" t="n">
-        <v>55000000</v>
+        <v>89324761.90476191</v>
       </c>
       <c r="G6" t="n">
-        <v>89324761.90476191</v>
+        <v>82500000</v>
       </c>
       <c r="H6" t="n">
-        <v>82500000</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>23533333.33333333</v>
       </c>
       <c r="J6" t="n">
-        <v>23533333.33333333</v>
+        <v>18333333.33333333</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>17737437.58823529</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>133064664.8333333</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>18333333.33333333</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>17737437.58823529</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="R6" t="n">
-        <v>133064664.8333333</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="W6" t="n">
         <v>73333333.33333333</v>
       </c>
     </row>
@@ -917,63 +897,60 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>225245.5</v>
       </c>
       <c r="E7" t="n">
-        <v>225245.5</v>
+        <v>55000000</v>
       </c>
       <c r="F7" t="n">
-        <v>55000000</v>
+        <v>88324761.90476191</v>
       </c>
       <c r="G7" t="n">
-        <v>88324761.90476191</v>
+        <v>82500000</v>
       </c>
       <c r="H7" t="n">
-        <v>82500000</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>23533333.33333333</v>
       </c>
       <c r="J7" t="n">
-        <v>23533333.33333333</v>
+        <v>18333333.33333333</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>53212312.76470588</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>133064664.8333333</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
         <v>18333333.33333333</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>53212312.76470588</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="R7" t="n">
-        <v>133064664.8333333</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
       <c r="V7" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="W7" t="n">
         <v>73333333.33333333</v>
       </c>
     </row>
@@ -988,63 +965,60 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>225245.5</v>
       </c>
       <c r="E8" t="n">
-        <v>225245.5</v>
+        <v>57224255.83333333</v>
       </c>
       <c r="F8" t="n">
-        <v>57224255.83333333</v>
+        <v>107535317.4603175</v>
       </c>
       <c r="G8" t="n">
-        <v>107535317.4603175</v>
+        <v>82500000</v>
       </c>
       <c r="H8" t="n">
-        <v>82500000</v>
+        <v>3333333.333333333</v>
       </c>
       <c r="I8" t="n">
-        <v>3333333.333333333</v>
+        <v>23533333.33333333</v>
       </c>
       <c r="J8" t="n">
-        <v>23533333.33333333</v>
+        <v>18333333.33333333</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>53212312.76470588</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1145833.333333333</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>133064664.8333333</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
         <v>18333333.33333333</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>53212312.76470588</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1145833.333333333</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="R8" t="n">
-        <v>133064664.8333333</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="W8" t="n">
         <v>73333333.33333333</v>
       </c>
     </row>
@@ -1059,63 +1033,60 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>225245.5</v>
       </c>
       <c r="E9" t="n">
-        <v>225245.5</v>
+        <v>61672767.49999999</v>
       </c>
       <c r="F9" t="n">
-        <v>61672767.49999999</v>
+        <v>258262218.0451128</v>
       </c>
       <c r="G9" t="n">
-        <v>258262218.0451128</v>
+        <v>82500000</v>
       </c>
       <c r="H9" t="n">
-        <v>82500000</v>
+        <v>10000000</v>
       </c>
       <c r="I9" t="n">
-        <v>10000000</v>
+        <v>27700000</v>
       </c>
       <c r="J9" t="n">
-        <v>27700000</v>
+        <v>18333333.33333333</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>53212312.76470588</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3437500</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>81445500.66666666</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>307692307.6923077</v>
+      </c>
+      <c r="U9" t="n">
         <v>18333333.33333333</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>53212312.76470588</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3437500</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="R9" t="n">
-        <v>81445500.66666666</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>307692307.6923077</v>
-      </c>
       <c r="V9" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="W9" t="n">
         <v>73333333.33333333</v>
       </c>
     </row>
@@ -1130,63 +1101,60 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>225245.5</v>
       </c>
       <c r="E10" t="n">
-        <v>225245.5</v>
+        <v>61672767.49999999</v>
       </c>
       <c r="F10" t="n">
-        <v>61672767.49999999</v>
+        <v>286539160.4010025</v>
       </c>
       <c r="G10" t="n">
-        <v>286539160.4010025</v>
+        <v>119166666.6666667</v>
       </c>
       <c r="H10" t="n">
-        <v>119166666.6666667</v>
+        <v>10000000</v>
       </c>
       <c r="I10" t="n">
-        <v>10000000</v>
+        <v>36033333.33333333</v>
       </c>
       <c r="J10" t="n">
-        <v>36033333.33333333</v>
+        <v>18333333.33333333</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>53212312.76470588</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5770833.333333333</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>55635918.58333333</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>307692307.6923077</v>
+      </c>
+      <c r="U10" t="n">
         <v>18333333.33333333</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>53212312.76470588</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5770833.333333333</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>55635918.58333333</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>307692307.6923077</v>
-      </c>
       <c r="V10" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="W10" t="n">
         <v>73333333.33333333</v>
       </c>
     </row>
@@ -1201,63 +1169,60 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>225245.5</v>
       </c>
       <c r="E11" t="n">
-        <v>225245.5</v>
+        <v>68894989.72222221</v>
       </c>
       <c r="F11" t="n">
-        <v>68894989.72222221</v>
+        <v>279813961.9883041</v>
       </c>
       <c r="G11" t="n">
-        <v>279813961.9883041</v>
+        <v>116111111.1111111</v>
       </c>
       <c r="H11" t="n">
-        <v>116111111.1111111</v>
+        <v>10000000</v>
       </c>
       <c r="I11" t="n">
-        <v>10000000</v>
+        <v>36033333.33333333</v>
       </c>
       <c r="J11" t="n">
-        <v>36033333.33333333</v>
+        <v>18333333.33333333</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>53212312.76470588</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5770833.333333333</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>55844251.91666666</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>310608974.3589743</v>
+      </c>
+      <c r="U11" t="n">
         <v>18333333.33333333</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>53212312.76470588</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5770833.333333333</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>55844251.91666666</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>310608974.3589743</v>
-      </c>
       <c r="V11" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="W11" t="n">
         <v>36666666.66666666</v>
       </c>
     </row>
@@ -1272,63 +1237,60 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>225245.5</v>
       </c>
       <c r="E12" t="n">
-        <v>225245.5</v>
+        <v>102573916.9583333</v>
       </c>
       <c r="F12" t="n">
-        <v>102573916.9583333</v>
+        <v>302077850.877193</v>
       </c>
       <c r="G12" t="n">
-        <v>302077850.877193</v>
+        <v>110000000</v>
       </c>
       <c r="H12" t="n">
-        <v>110000000</v>
+        <v>10000000</v>
       </c>
       <c r="I12" t="n">
-        <v>10000000</v>
+        <v>36033333.33333333</v>
       </c>
       <c r="J12" t="n">
-        <v>36033333.33333333</v>
+        <v>18333333.33333333</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>53212312.76470588</v>
+      </c>
+      <c r="M12" t="n">
+        <v>305770833.3333333</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>55844251.91666666</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>312067307.6923077</v>
+      </c>
+      <c r="U12" t="n">
         <v>18333333.33333333</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>53212312.76470588</v>
-      </c>
-      <c r="N12" t="n">
-        <v>305770833.3333333</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>55844251.91666666</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>312067307.6923077</v>
-      </c>
       <c r="V12" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="W12" t="n">
         <v>36666666.66666666</v>
       </c>
     </row>
@@ -1337,43 +1299,43 @@
         <v>43830</v>
       </c>
       <c r="B13" t="n">
-        <v>53.47222222222221</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>225245.5</v>
       </c>
       <c r="E13" t="n">
-        <v>225245.5</v>
+        <v>102573916.9583333</v>
       </c>
       <c r="F13" t="n">
-        <v>102573916.9583333</v>
+        <v>606387841.5401248</v>
       </c>
       <c r="G13" t="n">
-        <v>606387841.5401248</v>
+        <v>110000000</v>
       </c>
       <c r="H13" t="n">
-        <v>110000000</v>
+        <v>10000000</v>
       </c>
       <c r="I13" t="n">
-        <v>10000000</v>
+        <v>39366666.66666666</v>
       </c>
       <c r="J13" t="n">
-        <v>39366666.66666666</v>
+        <v>12222222.22222222</v>
       </c>
       <c r="K13" t="n">
-        <v>12222222.22222222</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>218086013.8897059</v>
       </c>
       <c r="M13" t="n">
-        <v>218086013.8897059</v>
+        <v>313270833.3333333</v>
       </c>
       <c r="N13" t="n">
-        <v>313270833.3333333</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1382,24 +1344,21 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>55844251.91666666</v>
       </c>
       <c r="R13" t="n">
-        <v>55844251.91666666</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>312067307.6923077</v>
       </c>
       <c r="U13" t="n">
-        <v>312067307.6923077</v>
+        <v>18333333.33333333</v>
       </c>
       <c r="V13" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="W13" t="n">
         <v>33611111.11111111</v>
       </c>
     </row>
@@ -1408,69 +1367,66 @@
         <v>43921</v>
       </c>
       <c r="B14" t="n">
-        <v>160.4166666666666</v>
+        <v>82500000</v>
       </c>
       <c r="C14" t="n">
-        <v>82500000</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>225245.5</v>
       </c>
       <c r="E14" t="n">
-        <v>225245.5</v>
+        <v>92551311.58333333</v>
       </c>
       <c r="F14" t="n">
-        <v>92551311.58333333</v>
+        <v>1376380748.959503</v>
       </c>
       <c r="G14" t="n">
-        <v>1376380748.959503</v>
+        <v>110000000</v>
       </c>
       <c r="H14" t="n">
-        <v>110000000</v>
+        <v>21111111.11111111</v>
       </c>
       <c r="I14" t="n">
-        <v>21111111.11111111</v>
+        <v>47144444.44444444</v>
       </c>
       <c r="J14" t="n">
-        <v>47144444.44444444</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>218086013.8897059</v>
       </c>
       <c r="M14" t="n">
-        <v>218086013.8897059</v>
+        <v>113270833.3333333</v>
       </c>
       <c r="N14" t="n">
-        <v>113270833.3333333</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="P14" t="n">
-        <v>1666666.666666667</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>62510918.58333334</v>
       </c>
       <c r="R14" t="n">
-        <v>62510918.58333334</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>312067307.6923077</v>
       </c>
       <c r="U14" t="n">
-        <v>312067307.6923077</v>
+        <v>18333333.33333333</v>
       </c>
       <c r="V14" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="W14" t="n">
         <v>27500000</v>
       </c>
     </row>
@@ -1479,69 +1435,66 @@
         <v>44012</v>
       </c>
       <c r="B15" t="n">
-        <v>160.4166666666666</v>
+        <v>247500000</v>
       </c>
       <c r="C15" t="n">
-        <v>247500000</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>225245.5</v>
       </c>
       <c r="E15" t="n">
-        <v>225245.5</v>
+        <v>72506100.83333333</v>
       </c>
       <c r="F15" t="n">
-        <v>72506100.83333333</v>
+        <v>1372111219.222661</v>
       </c>
       <c r="G15" t="n">
-        <v>1372111219.222661</v>
+        <v>110000000</v>
       </c>
       <c r="H15" t="n">
-        <v>110000000</v>
+        <v>43333333.33333334</v>
       </c>
       <c r="I15" t="n">
-        <v>43333333.33333334</v>
+        <v>49233333.33333333</v>
       </c>
       <c r="J15" t="n">
-        <v>49233333.33333333</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>218086013.8897059</v>
       </c>
       <c r="M15" t="n">
-        <v>218086013.8897059</v>
+        <v>16604166.66666667</v>
       </c>
       <c r="N15" t="n">
-        <v>16604166.66666667</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="P15" t="n">
-        <v>1666666.666666667</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>62510918.58333334</v>
       </c>
       <c r="R15" t="n">
-        <v>62510918.58333334</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>312067307.6923077</v>
       </c>
       <c r="U15" t="n">
-        <v>312067307.6923077</v>
+        <v>18333333.33333333</v>
       </c>
       <c r="V15" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="W15" t="n">
         <v>27500000</v>
       </c>
     </row>
@@ -1550,69 +1503,66 @@
         <v>44104</v>
       </c>
       <c r="B16" t="n">
-        <v>160.4166666666666</v>
+        <v>254375000</v>
       </c>
       <c r="C16" t="n">
-        <v>254375000</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>225245.5</v>
       </c>
       <c r="E16" t="n">
-        <v>225245.5</v>
+        <v>51948511.66666666</v>
       </c>
       <c r="F16" t="n">
-        <v>51948511.66666666</v>
+        <v>1446225220.973466</v>
       </c>
       <c r="G16" t="n">
-        <v>1446225220.973466</v>
+        <v>110000000</v>
       </c>
       <c r="H16" t="n">
-        <v>110000000</v>
+        <v>43333333.33333334</v>
       </c>
       <c r="I16" t="n">
-        <v>43333333.33333334</v>
+        <v>49166666.66666666</v>
       </c>
       <c r="J16" t="n">
-        <v>49166666.66666666</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>218086013.8897059</v>
       </c>
       <c r="M16" t="n">
-        <v>218086013.8897059</v>
+        <v>16604166.66666667</v>
       </c>
       <c r="N16" t="n">
-        <v>16604166.66666667</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="P16" t="n">
-        <v>1666666.666666667</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>62510918.58333334</v>
       </c>
       <c r="R16" t="n">
-        <v>62510918.58333334</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>312067307.6923077</v>
       </c>
       <c r="U16" t="n">
-        <v>312067307.6923077</v>
+        <v>18333333.33333333</v>
       </c>
       <c r="V16" t="n">
-        <v>18333333.33333333</v>
-      </c>
-      <c r="W16" t="n">
         <v>27500000</v>
       </c>
     </row>
@@ -1621,69 +1571,66 @@
         <v>44196</v>
       </c>
       <c r="B17" t="n">
-        <v>160.4166666666666</v>
+        <v>185625000</v>
       </c>
       <c r="C17" t="n">
-        <v>185625000</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>225245.5</v>
       </c>
       <c r="E17" t="n">
-        <v>225245.5</v>
+        <v>10833333.33333333</v>
       </c>
       <c r="F17" t="n">
-        <v>10833333.33333333</v>
+        <v>1450225220.973466</v>
       </c>
       <c r="G17" t="n">
-        <v>1450225220.973466</v>
+        <v>97777777.77777778</v>
       </c>
       <c r="H17" t="n">
-        <v>97777777.77777778</v>
+        <v>43333333.33333334</v>
       </c>
       <c r="I17" t="n">
-        <v>43333333.33333334</v>
+        <v>46666666.66666666</v>
       </c>
       <c r="J17" t="n">
-        <v>46666666.66666666</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>218086013.8897059</v>
       </c>
       <c r="M17" t="n">
-        <v>218086013.8897059</v>
+        <v>16604166.66666667</v>
       </c>
       <c r="N17" t="n">
-        <v>16604166.66666667</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="P17" t="n">
-        <v>1666666.666666667</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>13617877.56</v>
       </c>
       <c r="R17" t="n">
-        <v>13617877.56</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>312067307.6923077</v>
       </c>
       <c r="U17" t="n">
-        <v>312067307.6923077</v>
+        <v>12222222.22222222</v>
       </c>
       <c r="V17" t="n">
-        <v>12222222.22222222</v>
-      </c>
-      <c r="W17" t="n">
         <v>36666666.66666666</v>
       </c>
     </row>
@@ -1692,69 +1639,66 @@
         <v>44286</v>
       </c>
       <c r="B18" t="n">
-        <v>160.4166666666666</v>
+        <v>20625000</v>
       </c>
       <c r="C18" t="n">
-        <v>20625000</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>225245.5</v>
       </c>
       <c r="E18" t="n">
-        <v>225245.5</v>
+        <v>10833333.33333333</v>
       </c>
       <c r="F18" t="n">
-        <v>10833333.33333333</v>
+        <v>1409352205.10045</v>
       </c>
       <c r="G18" t="n">
-        <v>1409352205.10045</v>
+        <v>36666666.66666666</v>
       </c>
       <c r="H18" t="n">
-        <v>36666666.66666666</v>
+        <v>43333333.33333334</v>
       </c>
       <c r="I18" t="n">
-        <v>43333333.33333334</v>
+        <v>41666666.66666666</v>
       </c>
       <c r="J18" t="n">
-        <v>41666666.66666666</v>
+        <v>147392290</v>
       </c>
       <c r="K18" t="n">
-        <v>147392290</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>100750504.9402174</v>
       </c>
       <c r="M18" t="n">
-        <v>100750504.9402174</v>
+        <v>16604166.66666667</v>
       </c>
       <c r="N18" t="n">
-        <v>16604166.66666667</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="P18" t="n">
-        <v>1666666.666666667</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>27103632.68</v>
       </c>
       <c r="R18" t="n">
-        <v>27103632.68</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>312067307.6923077</v>
       </c>
       <c r="U18" t="n">
-        <v>312067307.6923077</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
         <v>55000000</v>
       </c>
     </row>
@@ -1763,69 +1707,66 @@
         <v>44377</v>
       </c>
       <c r="B19" t="n">
-        <v>160.4166666666666</v>
+        <v>20625000</v>
       </c>
       <c r="C19" t="n">
-        <v>20625000</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>10833333.33333333</v>
       </c>
       <c r="F19" t="n">
-        <v>10833333.33333333</v>
+        <v>1370141187.360021</v>
       </c>
       <c r="G19" t="n">
-        <v>1370141187.360021</v>
+        <v>36666666.66666666</v>
       </c>
       <c r="H19" t="n">
-        <v>36666666.66666666</v>
+        <v>43333333.33333334</v>
       </c>
       <c r="I19" t="n">
-        <v>43333333.33333334</v>
+        <v>41666666.66666666</v>
       </c>
       <c r="J19" t="n">
-        <v>41666666.66666666</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>45792604.56521739</v>
       </c>
       <c r="M19" t="n">
-        <v>45792604.56521739</v>
+        <v>16604166.66666667</v>
       </c>
       <c r="N19" t="n">
-        <v>16604166.66666667</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="P19" t="n">
-        <v>1666666.666666667</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>501859811.797647</v>
       </c>
       <c r="R19" t="n">
-        <v>501859811.797647</v>
+        <v>833333.3333333333</v>
       </c>
       <c r="S19" t="n">
-        <v>833333.3333333333</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>312067307.6923077</v>
       </c>
       <c r="U19" t="n">
-        <v>312067307.6923077</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
         <v>55000000</v>
       </c>
     </row>
@@ -1834,69 +1775,66 @@
         <v>44469</v>
       </c>
       <c r="B20" t="n">
-        <v>160.4166666666666</v>
+        <v>20625000</v>
       </c>
       <c r="C20" t="n">
-        <v>20625000</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>10833333.33333333</v>
       </c>
       <c r="F20" t="n">
-        <v>10833333.33333333</v>
+        <v>1364596742.915576</v>
       </c>
       <c r="G20" t="n">
-        <v>1364596742.915576</v>
+        <v>36666666.66666666</v>
       </c>
       <c r="H20" t="n">
-        <v>36666666.66666666</v>
+        <v>40000000</v>
       </c>
       <c r="I20" t="n">
-        <v>40000000</v>
+        <v>78333333.33333333</v>
       </c>
       <c r="J20" t="n">
-        <v>78333333.33333333</v>
+        <v>32468305.63636363</v>
       </c>
       <c r="K20" t="n">
-        <v>32468305.63636363</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>45792604.56521739</v>
       </c>
       <c r="M20" t="n">
-        <v>45792604.56521739</v>
+        <v>16847222.22222222</v>
       </c>
       <c r="N20" t="n">
-        <v>16847222.22222222</v>
+        <v>121111.1111111111</v>
       </c>
       <c r="O20" t="n">
-        <v>121111.1111111111</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="P20" t="n">
-        <v>1666666.666666667</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>501859811.797647</v>
       </c>
       <c r="R20" t="n">
-        <v>501859811.797647</v>
+        <v>1250000</v>
       </c>
       <c r="S20" t="n">
-        <v>1250000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>312067307.6923077</v>
       </c>
       <c r="U20" t="n">
-        <v>312067307.6923077</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
         <v>55000000</v>
       </c>
     </row>
@@ -1905,69 +1843,66 @@
         <v>44561</v>
       </c>
       <c r="B21" t="n">
-        <v>160.4166666666666</v>
+        <v>20625000</v>
       </c>
       <c r="C21" t="n">
-        <v>20625000</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>10833333.33333333</v>
       </c>
       <c r="F21" t="n">
-        <v>10833333.33333333</v>
+        <v>1170491187.360021</v>
       </c>
       <c r="G21" t="n">
-        <v>1170491187.360021</v>
+        <v>36666666.66666666</v>
       </c>
       <c r="H21" t="n">
-        <v>36666666.66666666</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="I21" t="n">
-        <v>33333333.33333334</v>
+        <v>147500000</v>
       </c>
       <c r="J21" t="n">
-        <v>147500000</v>
+        <v>91612761.38636363</v>
       </c>
       <c r="K21" t="n">
-        <v>91612761.38636363</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>149292604.5652174</v>
       </c>
       <c r="M21" t="n">
-        <v>149292604.5652174</v>
+        <v>17333333.33333334</v>
       </c>
       <c r="N21" t="n">
-        <v>17333333.33333334</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="O21" t="n">
-        <v>363333.3333333333</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="P21" t="n">
-        <v>1666666.666666667</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>501859811.797647</v>
       </c>
       <c r="R21" t="n">
-        <v>501859811.797647</v>
+        <v>1250000</v>
       </c>
       <c r="S21" t="n">
-        <v>1250000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>379904951.3589743</v>
       </c>
       <c r="U21" t="n">
-        <v>379904951.3589743</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
         <v>55000000</v>
       </c>
     </row>
@@ -1976,69 +1911,66 @@
         <v>44651</v>
       </c>
       <c r="B22" t="n">
-        <v>160.4166666666666</v>
+        <v>20625000</v>
       </c>
       <c r="C22" t="n">
-        <v>20625000</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>10833333.33333333</v>
       </c>
       <c r="F22" t="n">
-        <v>10833333.33333333</v>
+        <v>874580930.9497645</v>
       </c>
       <c r="G22" t="n">
-        <v>874580930.9497645</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="I22" t="n">
-        <v>33333333.33333334</v>
+        <v>139166666.6666667</v>
       </c>
       <c r="J22" t="n">
-        <v>139166666.6666667</v>
+        <v>91612761.38636363</v>
       </c>
       <c r="K22" t="n">
-        <v>91612761.38636363</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>107011354.5652174</v>
       </c>
       <c r="M22" t="n">
-        <v>107011354.5652174</v>
+        <v>15000000</v>
       </c>
       <c r="N22" t="n">
-        <v>15000000</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="O22" t="n">
-        <v>363333.3333333333</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="P22" t="n">
-        <v>1666666.666666667</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>501859811.797647</v>
       </c>
       <c r="R22" t="n">
-        <v>501859811.797647</v>
+        <v>1250000</v>
       </c>
       <c r="S22" t="n">
-        <v>1250000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>108879310.3333333</v>
       </c>
       <c r="U22" t="n">
-        <v>108879310.3333333</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
         <v>55000000</v>
       </c>
     </row>
@@ -2047,69 +1979,66 @@
         <v>44742</v>
       </c>
       <c r="B23" t="n">
-        <v>160.4166666666666</v>
+        <v>20625000</v>
       </c>
       <c r="C23" t="n">
-        <v>20625000</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>13591756.27240143</v>
       </c>
       <c r="F23" t="n">
-        <v>13591756.27240143</v>
+        <v>467295140.3514739</v>
       </c>
       <c r="G23" t="n">
-        <v>467295140.3514739</v>
+        <v>11111111.11111111</v>
       </c>
       <c r="H23" t="n">
-        <v>11111111.11111111</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="I23" t="n">
-        <v>33333333.33333334</v>
+        <v>335320512.8205128</v>
       </c>
       <c r="J23" t="n">
-        <v>335320512.8205128</v>
+        <v>81019159.50757575</v>
       </c>
       <c r="K23" t="n">
-        <v>81019159.50757575</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>268641162.2575251</v>
       </c>
       <c r="M23" t="n">
-        <v>268641162.2575251</v>
+        <v>15000000</v>
       </c>
       <c r="N23" t="n">
-        <v>15000000</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="O23" t="n">
-        <v>363333.3333333333</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="P23" t="n">
-        <v>1666666.666666667</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>508318145.1309803</v>
       </c>
       <c r="R23" t="n">
-        <v>508318145.1309803</v>
+        <v>1250000</v>
       </c>
       <c r="S23" t="n">
-        <v>1250000</v>
+        <v>12777777.77777778</v>
       </c>
       <c r="T23" t="n">
-        <v>12777777.77777778</v>
+        <v>105962643.6666667</v>
       </c>
       <c r="U23" t="n">
-        <v>105962643.6666667</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
         <v>55000000</v>
       </c>
     </row>
@@ -2118,69 +2047,66 @@
         <v>44834</v>
       </c>
       <c r="B24" t="n">
-        <v>160.4166666666666</v>
+        <v>20625000</v>
       </c>
       <c r="C24" t="n">
-        <v>20625000</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>14970967.74193548</v>
       </c>
       <c r="F24" t="n">
-        <v>14970967.74193548</v>
+        <v>665864584.7959183</v>
       </c>
       <c r="G24" t="n">
-        <v>665864584.7959183</v>
+        <v>11111111.11111111</v>
       </c>
       <c r="H24" t="n">
-        <v>11111111.11111111</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="I24" t="n">
-        <v>33333333.33333334</v>
+        <v>335320512.8205128</v>
       </c>
       <c r="J24" t="n">
-        <v>335320512.8205128</v>
+        <v>99722848.30555555</v>
       </c>
       <c r="K24" t="n">
-        <v>99722848.30555555</v>
+        <v>5555555.555555556</v>
       </c>
       <c r="L24" t="n">
-        <v>5555555.555555556</v>
+        <v>360275777.6421405</v>
       </c>
       <c r="M24" t="n">
-        <v>360275777.6421405</v>
+        <v>15000000</v>
       </c>
       <c r="N24" t="n">
-        <v>15000000</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="O24" t="n">
-        <v>363333.3333333333</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="P24" t="n">
-        <v>1666666.666666667</v>
+        <v>7800000</v>
       </c>
       <c r="Q24" t="n">
-        <v>7800000</v>
+        <v>363399418.7584313</v>
       </c>
       <c r="R24" t="n">
-        <v>363399418.7584313</v>
+        <v>1250000</v>
       </c>
       <c r="S24" t="n">
-        <v>1250000</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="T24" t="n">
-        <v>19166666.66666667</v>
+        <v>104504310.3333333</v>
       </c>
       <c r="U24" t="n">
-        <v>104504310.3333333</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
         <v>55000000</v>
       </c>
     </row>
@@ -2189,69 +2115,66 @@
         <v>44926</v>
       </c>
       <c r="B25" t="n">
-        <v>106.9444444444444</v>
+        <v>20625000</v>
       </c>
       <c r="C25" t="n">
-        <v>20625000</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>14970967.74193548</v>
       </c>
       <c r="F25" t="n">
-        <v>14970967.74193548</v>
+        <v>646003473.6848073</v>
       </c>
       <c r="G25" t="n">
-        <v>646003473.6848073</v>
+        <v>11111111.11111111</v>
       </c>
       <c r="H25" t="n">
-        <v>11111111.11111111</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="I25" t="n">
-        <v>33333333.33333334</v>
+        <v>303653846.1538461</v>
       </c>
       <c r="J25" t="n">
-        <v>303653846.1538461</v>
+        <v>125421300.0833333</v>
       </c>
       <c r="K25" t="n">
-        <v>125421300.0833333</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="L25" t="n">
-        <v>8333333.333333334</v>
+        <v>383805189.4068464</v>
       </c>
       <c r="M25" t="n">
-        <v>383805189.4068464</v>
+        <v>7500000</v>
       </c>
       <c r="N25" t="n">
-        <v>7500000</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="O25" t="n">
-        <v>363333.3333333333</v>
+        <v>1666666.666666667</v>
       </c>
       <c r="P25" t="n">
-        <v>1666666.666666667</v>
+        <v>212055315.9047619</v>
       </c>
       <c r="Q25" t="n">
-        <v>212055315.9047619</v>
+        <v>59016511.46787879</v>
       </c>
       <c r="R25" t="n">
-        <v>59016511.46787879</v>
+        <v>1250000</v>
       </c>
       <c r="S25" t="n">
-        <v>1250000</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="T25" t="n">
-        <v>19166666.66666667</v>
+        <v>104504310.3333333</v>
       </c>
       <c r="U25" t="n">
-        <v>104504310.3333333</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
         <v>55000000</v>
       </c>
     </row>
@@ -2260,69 +2183,66 @@
         <v>45016</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>20625000</v>
       </c>
       <c r="C26" t="n">
-        <v>20625000</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>14970967.74193548</v>
       </c>
       <c r="F26" t="n">
-        <v>14970967.74193548</v>
+        <v>625940342.371676</v>
       </c>
       <c r="G26" t="n">
-        <v>625940342.371676</v>
+        <v>219444444.4444444</v>
       </c>
       <c r="H26" t="n">
-        <v>219444444.4444444</v>
+        <v>22222222.22222222</v>
       </c>
       <c r="I26" t="n">
-        <v>22222222.22222222</v>
+        <v>226709401.7094017</v>
       </c>
       <c r="J26" t="n">
-        <v>226709401.7094017</v>
+        <v>127620574.4722222</v>
       </c>
       <c r="K26" t="n">
-        <v>127620574.4722222</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="L26" t="n">
-        <v>8333333.333333334</v>
+        <v>395569895.2891994</v>
       </c>
       <c r="M26" t="n">
-        <v>395569895.2891994</v>
+        <v>7500000</v>
       </c>
       <c r="N26" t="n">
-        <v>7500000</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="O26" t="n">
-        <v>363333.3333333333</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>306382973.8571428</v>
       </c>
       <c r="Q26" t="n">
-        <v>306382973.8571428</v>
+        <v>38181818.18181818</v>
       </c>
       <c r="R26" t="n">
-        <v>38181818.18181818</v>
+        <v>1250000</v>
       </c>
       <c r="S26" t="n">
-        <v>1250000</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="T26" t="n">
-        <v>19166666.66666667</v>
+        <v>104504310.3333333</v>
       </c>
       <c r="U26" t="n">
-        <v>104504310.3333333</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
         <v>55000000</v>
       </c>
     </row>
@@ -2331,69 +2251,66 @@
         <v>45107</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>20625000</v>
       </c>
       <c r="C27" t="n">
-        <v>20625000</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>16685253.4562212</v>
       </c>
       <c r="F27" t="n">
-        <v>16685253.4562212</v>
+        <v>571300714.7454133</v>
       </c>
       <c r="G27" t="n">
-        <v>571300714.7454133</v>
+        <v>636111111.111111</v>
       </c>
       <c r="H27" t="n">
-        <v>636111111.111111</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>133717948.7179487</v>
       </c>
       <c r="J27" t="n">
-        <v>133717948.7179487</v>
+        <v>128720211.6666667</v>
       </c>
       <c r="K27" t="n">
-        <v>128720211.6666667</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="L27" t="n">
-        <v>8333333.333333334</v>
+        <v>456236561.955866</v>
       </c>
       <c r="M27" t="n">
-        <v>456236561.955866</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="N27" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="O27" t="n">
-        <v>363333.3333333333</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>306382973.8571428</v>
       </c>
       <c r="Q27" t="n">
-        <v>306382973.8571428</v>
+        <v>38181818.18181818</v>
       </c>
       <c r="R27" t="n">
-        <v>38181818.18181818</v>
+        <v>21083333.33333334</v>
       </c>
       <c r="S27" t="n">
-        <v>21083333.33333334</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="T27" t="n">
-        <v>19166666.66666667</v>
+        <v>104504310.3333333</v>
       </c>
       <c r="U27" t="n">
-        <v>104504310.3333333</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
         <v>55000000</v>
       </c>
     </row>
@@ -2402,69 +2319,66 @@
         <v>45199</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>13750000</v>
       </c>
       <c r="C28" t="n">
-        <v>13750000</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>20113824.88479263</v>
       </c>
       <c r="F28" t="n">
-        <v>20113824.88479263</v>
+        <v>601522350.7584852</v>
       </c>
       <c r="G28" t="n">
-        <v>601522350.7584852</v>
+        <v>681111111.111111</v>
       </c>
       <c r="H28" t="n">
-        <v>681111111.111111</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>148638888.8888889</v>
       </c>
       <c r="J28" t="n">
-        <v>148638888.8888889</v>
+        <v>128720211.6666667</v>
       </c>
       <c r="K28" t="n">
-        <v>128720211.6666667</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="L28" t="n">
-        <v>8333333.333333334</v>
+        <v>456236561.955866</v>
       </c>
       <c r="M28" t="n">
-        <v>456236561.955866</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="N28" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="O28" t="n">
-        <v>363333.3333333333</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>306382973.8571428</v>
       </c>
       <c r="Q28" t="n">
-        <v>306382973.8571428</v>
+        <v>38181818.18181818</v>
       </c>
       <c r="R28" t="n">
-        <v>38181818.18181818</v>
+        <v>21083333.33333334</v>
       </c>
       <c r="S28" t="n">
-        <v>21083333.33333334</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="T28" t="n">
-        <v>19166666.66666667</v>
+        <v>104504310.3333333</v>
       </c>
       <c r="U28" t="n">
-        <v>104504310.3333333</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
         <v>55000000</v>
       </c>
     </row>
@@ -2482,60 +2396,57 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>20113824.88479263</v>
       </c>
       <c r="F29" t="n">
-        <v>20113824.88479263</v>
+        <v>606966795.2029296</v>
       </c>
       <c r="G29" t="n">
-        <v>606966795.2029296</v>
+        <v>681111111.111111</v>
       </c>
       <c r="H29" t="n">
-        <v>681111111.111111</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>283036549.7076024</v>
       </c>
       <c r="J29" t="n">
-        <v>283036549.7076024</v>
+        <v>128720211.6666667</v>
       </c>
       <c r="K29" t="n">
-        <v>128720211.6666667</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="L29" t="n">
-        <v>8333333.333333334</v>
+        <v>648229282.6503105</v>
       </c>
       <c r="M29" t="n">
-        <v>648229282.6503105</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="N29" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="O29" t="n">
-        <v>363333.3333333333</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>306382973.8571428</v>
       </c>
       <c r="Q29" t="n">
-        <v>306382973.8571428</v>
+        <v>38181818.18181818</v>
       </c>
       <c r="R29" t="n">
-        <v>38181818.18181818</v>
+        <v>21083333.33333334</v>
       </c>
       <c r="S29" t="n">
-        <v>21083333.33333334</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="T29" t="n">
-        <v>19166666.66666667</v>
+        <v>104504310.3333333</v>
       </c>
       <c r="U29" t="n">
-        <v>104504310.3333333</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
         <v>36666666.66666666</v>
       </c>
     </row>
@@ -2553,60 +2464,57 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>14970967.74193548</v>
       </c>
       <c r="F30" t="n">
-        <v>14970967.74193548</v>
+        <v>594466795.2029296</v>
       </c>
       <c r="G30" t="n">
-        <v>594466795.2029296</v>
+        <v>681111111.111111</v>
       </c>
       <c r="H30" t="n">
-        <v>681111111.111111</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>347013157.8947368</v>
       </c>
       <c r="J30" t="n">
-        <v>347013157.8947368</v>
+        <v>387479203.5555556</v>
       </c>
       <c r="K30" t="n">
-        <v>387479203.5555556</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="L30" t="n">
-        <v>8333333.333333334</v>
+        <v>870451504.8725327</v>
       </c>
       <c r="M30" t="n">
-        <v>870451504.8725327</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="N30" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="O30" t="n">
-        <v>363333.3333333333</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>306382973.8571428</v>
       </c>
       <c r="Q30" t="n">
-        <v>306382973.8571428</v>
+        <v>38181818.18181818</v>
       </c>
       <c r="R30" t="n">
-        <v>38181818.18181818</v>
+        <v>21083333.33333334</v>
       </c>
       <c r="S30" t="n">
-        <v>21083333.33333334</v>
+        <v>19166666.66666667</v>
       </c>
       <c r="T30" t="n">
-        <v>19166666.66666667</v>
+        <v>104504310.3333333</v>
       </c>
       <c r="U30" t="n">
-        <v>104504310.3333333</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2624,60 +2532,57 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>14970967.74193548</v>
       </c>
       <c r="F31" t="n">
-        <v>14970967.74193548</v>
+        <v>545022350.7584851</v>
       </c>
       <c r="G31" t="n">
-        <v>545022350.7584851</v>
+        <v>837602339.1812865</v>
       </c>
       <c r="H31" t="n">
-        <v>837602339.1812865</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>363679824.5614035</v>
       </c>
       <c r="J31" t="n">
-        <v>363679824.5614035</v>
+        <v>516858699.5000001</v>
       </c>
       <c r="K31" t="n">
-        <v>516858699.5000001</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="L31" t="n">
-        <v>8333333.333333334</v>
+        <v>870451504.8725327</v>
       </c>
       <c r="M31" t="n">
-        <v>870451504.8725327</v>
+        <v>4166666.666666667</v>
       </c>
       <c r="N31" t="n">
-        <v>4166666.666666667</v>
+        <v>363333.3333333333</v>
       </c>
       <c r="O31" t="n">
-        <v>363333.3333333333</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>306382973.8571428</v>
       </c>
       <c r="Q31" t="n">
-        <v>306382973.8571428</v>
+        <v>38181818.18181818</v>
       </c>
       <c r="R31" t="n">
-        <v>38181818.18181818</v>
+        <v>20250000</v>
       </c>
       <c r="S31" t="n">
-        <v>20250000</v>
+        <v>52500000</v>
       </c>
       <c r="T31" t="n">
-        <v>52500000</v>
+        <v>104504310.3333333</v>
       </c>
       <c r="U31" t="n">
-        <v>104504310.3333333</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
         <v>100000000</v>
       </c>
     </row>
@@ -2695,60 +2600,57 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>14970967.74193548</v>
       </c>
       <c r="F32" t="n">
-        <v>14970967.74193548</v>
+        <v>504194913.1167618</v>
       </c>
       <c r="G32" t="n">
-        <v>504194913.1167618</v>
+        <v>922913336.5146199</v>
       </c>
       <c r="H32" t="n">
-        <v>922913336.5146199</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>363679824.5614035</v>
       </c>
       <c r="J32" t="n">
-        <v>363679824.5614035</v>
+        <v>536170007.0833334</v>
       </c>
       <c r="K32" t="n">
-        <v>536170007.0833334</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="L32" t="n">
-        <v>8333333.333333334</v>
+        <v>870451504.8725327</v>
       </c>
       <c r="M32" t="n">
-        <v>870451504.8725327</v>
+        <v>2777777.777777778</v>
       </c>
       <c r="N32" t="n">
-        <v>2777777.777777778</v>
+        <v>242222.2222222222</v>
       </c>
       <c r="O32" t="n">
-        <v>242222.2222222222</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>117727657.9523809</v>
       </c>
       <c r="Q32" t="n">
-        <v>117727657.9523809</v>
+        <v>39433383.76515152</v>
       </c>
       <c r="R32" t="n">
-        <v>39433383.76515152</v>
+        <v>19833333.33333333</v>
       </c>
       <c r="S32" t="n">
-        <v>19833333.33333333</v>
+        <v>52500000</v>
       </c>
       <c r="T32" t="n">
-        <v>52500000</v>
+        <v>104504310.3333333</v>
       </c>
       <c r="U32" t="n">
-        <v>104504310.3333333</v>
+        <v>50416666.66666667</v>
       </c>
       <c r="V32" t="n">
-        <v>50416666.66666667</v>
-      </c>
-      <c r="W32" t="n">
         <v>100000000</v>
       </c>
     </row>
@@ -2766,31 +2668,31 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>9980645.161290323</v>
       </c>
       <c r="F33" t="n">
-        <v>9980645.161290323</v>
+        <v>470513220.439691</v>
       </c>
       <c r="G33" t="n">
-        <v>470513220.439691</v>
+        <v>922913336.5146199</v>
       </c>
       <c r="H33" t="n">
-        <v>922913336.5146199</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>363679824.5614035</v>
       </c>
       <c r="J33" t="n">
-        <v>363679824.5614035</v>
+        <v>477025551.3333333</v>
       </c>
       <c r="K33" t="n">
-        <v>477025551.3333333</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="L33" t="n">
-        <v>8333333.333333334</v>
+        <v>734985601.8290544</v>
       </c>
       <c r="M33" t="n">
-        <v>734985601.8290544</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2802,24 +2704,21 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>39433383.76515152</v>
       </c>
       <c r="R33" t="n">
-        <v>39433383.76515152</v>
+        <v>19833333.33333333</v>
       </c>
       <c r="S33" t="n">
-        <v>19833333.33333333</v>
+        <v>52500000</v>
       </c>
       <c r="T33" t="n">
-        <v>52500000</v>
+        <v>36666666.66666666</v>
       </c>
       <c r="U33" t="n">
-        <v>36666666.66666666</v>
+        <v>50416666.66666667</v>
       </c>
       <c r="V33" t="n">
-        <v>50416666.66666667</v>
-      </c>
-      <c r="W33" t="n">
         <v>134166666.6666667</v>
       </c>
     </row>
@@ -2840,28 +2739,28 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>357916666.6666666</v>
       </c>
       <c r="G34" t="n">
-        <v>357916666.6666666</v>
+        <v>907913336.5146199</v>
       </c>
       <c r="H34" t="n">
-        <v>907913336.5146199</v>
+        <v>22222222.22222222</v>
       </c>
       <c r="I34" t="n">
-        <v>22222222.22222222</v>
+        <v>363679824.5614035</v>
       </c>
       <c r="J34" t="n">
-        <v>363679824.5614035</v>
+        <v>477025551.3333333</v>
       </c>
       <c r="K34" t="n">
-        <v>477025551.3333333</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="L34" t="n">
-        <v>8333333.333333334</v>
+        <v>662002650.3073151</v>
       </c>
       <c r="M34" t="n">
-        <v>662002650.3073151</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2873,24 +2772,21 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>39433383.76515152</v>
       </c>
       <c r="R34" t="n">
-        <v>39433383.76515152</v>
+        <v>130944444.4444444</v>
       </c>
       <c r="S34" t="n">
-        <v>130944444.4444444</v>
+        <v>52500000</v>
       </c>
       <c r="T34" t="n">
-        <v>52500000</v>
+        <v>218519052.6666667</v>
       </c>
       <c r="U34" t="n">
-        <v>218519052.6666667</v>
+        <v>50416666.66666667</v>
       </c>
       <c r="V34" t="n">
-        <v>50416666.66666667</v>
-      </c>
-      <c r="W34" t="n">
         <v>202500000</v>
       </c>
     </row>
@@ -2902,37 +2798,37 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>44964000</v>
       </c>
       <c r="D35" t="n">
-        <v>44964000</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>267361111.1111111</v>
       </c>
       <c r="G35" t="n">
-        <v>267361111.1111111</v>
+        <v>866802225.4035087</v>
       </c>
       <c r="H35" t="n">
-        <v>866802225.4035087</v>
+        <v>66666666.66666667</v>
       </c>
       <c r="I35" t="n">
-        <v>66666666.66666667</v>
+        <v>299925438.5964912</v>
       </c>
       <c r="J35" t="n">
-        <v>299925438.5964912</v>
+        <v>476796384.6666666</v>
       </c>
       <c r="K35" t="n">
-        <v>476796384.6666666</v>
+        <v>8333333.333333334</v>
       </c>
       <c r="L35" t="n">
-        <v>8333333.333333334</v>
+        <v>1098391539.196204</v>
       </c>
       <c r="M35" t="n">
-        <v>1098391539.196204</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2944,24 +2840,21 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>32766717.09848485</v>
       </c>
       <c r="R35" t="n">
-        <v>32766717.09848485</v>
+        <v>232333333.3333333</v>
       </c>
       <c r="S35" t="n">
-        <v>232333333.3333333</v>
+        <v>39722222.22222222</v>
       </c>
       <c r="T35" t="n">
-        <v>39722222.22222222</v>
+        <v>218519052.6666667</v>
       </c>
       <c r="U35" t="n">
-        <v>218519052.6666667</v>
+        <v>50416666.66666667</v>
       </c>
       <c r="V35" t="n">
-        <v>50416666.66666667</v>
-      </c>
-      <c r="W35" t="n">
         <v>202500000</v>
       </c>
     </row>
@@ -2973,37 +2866,37 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>120000000</v>
       </c>
       <c r="D36" t="n">
-        <v>120000000</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>77752777.77777778</v>
       </c>
       <c r="G36" t="n">
-        <v>77752777.77777778</v>
+        <v>866802225.4035087</v>
       </c>
       <c r="H36" t="n">
-        <v>866802225.4035087</v>
+        <v>66666666.66666667</v>
       </c>
       <c r="I36" t="n">
-        <v>66666666.66666667</v>
+        <v>43083333.33333333</v>
       </c>
       <c r="J36" t="n">
-        <v>43083333.33333333</v>
+        <v>436447158.7777778</v>
       </c>
       <c r="K36" t="n">
-        <v>436447158.7777778</v>
+        <v>2777777.777777778</v>
       </c>
       <c r="L36" t="n">
-        <v>2777777.777777778</v>
+        <v>1263795636.732655</v>
       </c>
       <c r="M36" t="n">
-        <v>1263795636.732655</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -3015,24 +2908,21 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>7312171.643939395</v>
       </c>
       <c r="R36" t="n">
-        <v>7312171.643939395</v>
+        <v>232333333.3333333</v>
       </c>
       <c r="S36" t="n">
-        <v>232333333.3333333</v>
+        <v>33333333.33333334</v>
       </c>
       <c r="T36" t="n">
-        <v>33333333.33333334</v>
+        <v>218519052.6666667</v>
       </c>
       <c r="U36" t="n">
-        <v>218519052.6666667</v>
+        <v>50416666.66666667</v>
       </c>
       <c r="V36" t="n">
-        <v>50416666.66666667</v>
-      </c>
-      <c r="W36" t="n">
         <v>202500000</v>
       </c>
     </row>
